--- a/outputs/benchmark-beaters/Benchmark_Beaters_2026-09-16.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_2026-09-16.xlsx
@@ -2071,7 +2071,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46281.63539055427</v>
+        <v>46281.69288846787</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46281.63539055427</v>
+        <v>46281.69288846787</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.712</v>
+        <v>0.708</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>590.9299999999999</v>
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.552</v>
+        <v>0.527</v>
       </c>
       <c r="H9" s="124" t="n">
         <v>2723.16</v>
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.528</v>
+        <v>0.51</v>
       </c>
       <c r="H10" s="119" t="n">
         <v>1074.11</v>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.476</v>
+        <v>0.472</v>
       </c>
       <c r="H11" s="124" t="n">
         <v>12965.18</v>
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.428</v>
+        <v>0.422</v>
       </c>
       <c r="H12" s="119" t="n">
         <v>106366.17</v>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.374</v>
+        <v>0.375</v>
       </c>
       <c r="H13" s="124" t="n">
         <v>1241.31</v>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.34</v>
+        <v>0.347</v>
       </c>
       <c r="H14" s="119" t="n">
         <v>52717.24</v>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.307</v>
+        <v>0.316</v>
       </c>
       <c r="H15" s="124" t="n">
         <v>1165.85</v>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.296</v>
+        <v>0.289</v>
       </c>
       <c r="H16" s="119" t="n">
         <v>2992.18</v>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.246</v>
+        <v>0.252</v>
       </c>
       <c r="H18" s="119" t="n">
         <v>238.15</v>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.198</v>
+        <v>0.203</v>
       </c>
       <c r="H19" s="124" t="n">
         <v>1399.1</v>
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.145</v>
+        <v>0.155</v>
       </c>
       <c r="H21" s="124" t="n">
         <v>399.81</v>
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.133</v>
+        <v>0.131</v>
       </c>
       <c r="H22" s="119" t="n">
         <v>2198.74</v>
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>1.318</v>
+        <v>1.284</v>
       </c>
       <c r="H23" s="124" t="n">
         <v>754.02</v>
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.387</v>
+        <v>0.373</v>
       </c>
       <c r="H25" s="124" t="n">
         <v>1187.51</v>
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.286</v>
+        <v>0.287</v>
       </c>
       <c r="H26" s="119" t="n">
         <v>13692.85</v>
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.702</v>
+        <v>0.698</v>
       </c>
       <c r="H27" s="124" t="n">
         <v>627.4299999999999</v>
@@ -3086,7 +3086,7 @@
         </is>
       </c>
       <c r="G28" s="133" t="n">
-        <v>0.388</v>
+        <v>0.395</v>
       </c>
       <c r="H28" s="134" t="n">
         <v>706.29</v>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46281.63539055427</v>
+        <v>46281.69288846787</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>1.393</v>
+        <v>1.376</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>184733.62</v>
@@ -4543,7 +4543,7 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>1.124</v>
+        <v>1.109</v>
       </c>
       <c r="H9" s="124" t="n">
         <v>111614.59</v>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.613</v>
+        <v>0.603</v>
       </c>
       <c r="H10" s="119" t="n">
         <v>9525.209999999999</v>
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.538</v>
+        <v>0.55</v>
       </c>
       <c r="H11" s="124" t="n">
         <v>50462.03</v>
@@ -4666,7 +4666,7 @@
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.514</v>
+        <v>0.513</v>
       </c>
       <c r="H12" s="119" t="n">
         <v>18710.64</v>
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.416</v>
+        <v>0.414</v>
       </c>
       <c r="H13" s="124" t="n">
         <v>23983.85</v>
@@ -4748,7 +4748,7 @@
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.41</v>
+        <v>0.408</v>
       </c>
       <c r="H14" s="119" t="n">
         <v>36459.35</v>
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.363</v>
+        <v>0.367</v>
       </c>
       <c r="H15" s="124" t="n">
         <v>208163.39</v>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.307</v>
+        <v>0.305</v>
       </c>
       <c r="H16" s="119" t="n">
         <v>22431.33</v>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.277</v>
+        <v>0.272</v>
       </c>
       <c r="H17" s="124" t="n">
         <v>25502.21</v>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.27</v>
+        <v>0.267</v>
       </c>
       <c r="H18" s="119" t="n">
         <v>17599.83</v>
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.265</v>
+        <v>0.259</v>
       </c>
       <c r="H19" s="124" t="n">
         <v>47371.17</v>
@@ -4994,7 +4994,7 @@
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>2.637</v>
+        <v>2.621</v>
       </c>
       <c r="H20" s="119" t="n">
         <v>272918.28</v>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>1.666</v>
+        <v>1.683</v>
       </c>
       <c r="H21" s="124" t="n">
         <v>63016.2</v>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.869</v>
+        <v>0.859</v>
       </c>
       <c r="H22" s="119" t="n">
         <v>24056.52</v>
@@ -5117,7 +5117,7 @@
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.787</v>
+        <v>0.805</v>
       </c>
       <c r="H23" s="124" t="n">
         <v>91152.84</v>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.676</v>
+        <v>0.696</v>
       </c>
       <c r="H24" s="119" t="n">
         <v>90462.64999999999</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H25" s="124" t="n">
         <v>12100.89</v>
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.628</v>
+        <v>0.631</v>
       </c>
       <c r="H26" s="119" t="n">
         <v>35144.8</v>
@@ -5281,7 +5281,7 @@
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.519</v>
+        <v>0.534</v>
       </c>
       <c r="H27" s="124" t="n">
         <v>83426.56</v>
@@ -5322,7 +5322,7 @@
         </is>
       </c>
       <c r="G28" s="133" t="n">
-        <v>0.482</v>
+        <v>0.481</v>
       </c>
       <c r="H28" s="134" t="n">
         <v>16130.17</v>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_2026-09-16.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_2026-09-16.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
@@ -2071,7 +2071,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46281.69288846787</v>
+        <v>46281.72427577974</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46281.69288846787</v>
+        <v>46281.72427577974</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2238,7 +2238,7 @@
       <c r="J7" s="26" t="n"/>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="70" customHeight="1">
+    <row r="8" ht="52" customHeight="1">
       <c r="A8" s="36" t="n"/>
       <c r="B8" s="126" t="inlineStr">
         <is>
@@ -2247,39 +2247,39 @@
       </c>
       <c r="C8" s="115" t="inlineStr">
         <is>
-          <t>IFP</t>
+          <t>CVVY</t>
         </is>
       </c>
       <c r="D8" s="116" t="inlineStr">
         <is>
-          <t>Interfor Corporation</t>
+          <t>Cavvy Energy Ltd.</t>
         </is>
       </c>
       <c r="E8" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F8" s="117" t="inlineStr">
         <is>
-          <t>Paper and Forest Products</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.708</v>
+        <v>0.931</v>
       </c>
       <c r="H8" s="119" t="n">
-        <v>590.9299999999999</v>
+        <v>372.96</v>
       </c>
       <c r="I8" s="120" t="inlineStr">
         <is>
-          <t>Interfor Corporation together with its subsidiaries produces and sells wood products in Canada the United States Japan China Taiwan and internationally</t>
+          <t>Cavvy Energy Ltd operates as a midstream and upstream energy company in Canada</t>
         </is>
       </c>
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="52" customHeight="1">
+    <row r="9" ht="70" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="126" t="inlineStr">
         <is>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>WDO</t>
+          <t>IFP</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>Wesdome Gold Mines Ltd.</t>
+          <t>Interfor Corporation</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
@@ -2303,18 +2303,18 @@
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Paper and Forest Products</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.527</v>
+        <v>0.715</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>2723.16</v>
+        <v>590.9299999999999</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>Wesdome Gold Mines Ltd mines develops and explores for gold and silver deposits in Canada</t>
+          <t>Interfor Corporation together with its subsidiaries produces and sells wood products in Canada the United States Japan China Taiwan and internationally</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
@@ -2329,12 +2329,12 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>WDO</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Orezone Gold Corporation</t>
+          <t>Wesdome Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
@@ -2348,20 +2348,20 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.51</v>
+        <v>0.539</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>1074.11</v>
+        <v>2723.16</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Orezone Gold Corporation engages in the mining exploration and development of gold properties</t>
+          <t>Wesdome Gold Mines Ltd mines develops and explores for gold and silver deposits in Canada</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="70" customHeight="1">
+    <row r="11" ht="52" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="126" t="inlineStr">
         <is>
@@ -2370,33 +2370,33 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>IAG</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>iA Financial Corporation Inc.</t>
+          <t>Orezone Gold Corporation</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.472</v>
+        <v>0.51</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>12965.18</v>
+        <v>1074.11</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
+          <t>Orezone Gold Corporation engages in the mining exploration and development of gold properties</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>IAG</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia</t>
+          <t>iA Financial Corporation Inc.</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
@@ -2426,24 +2426,24 @@
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.422</v>
+        <v>0.474</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>106366.17</v>
+        <v>12965.18</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
+          <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="88" customHeight="1">
+    <row r="13" ht="70" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -2452,33 +2452,33 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>JWEL</t>
+          <t>BNS</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Jamieson Wellness Inc.</t>
+          <t>The Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Personal Care Products</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.375</v>
+        <v>0.422</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>1241.31</v>
+        <v>106366.17</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Jamieson Wellness Inc together with its subsidiaries develops manufactures distributes markets and sells the natural health products for human in Canada the United States China and internationally</t>
+          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
@@ -2493,39 +2493,39 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>JWEL</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Cenovus Energy Inc.</t>
+          <t>Jamieson Wellness Inc.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Personal Care Products</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.347</v>
+        <v>0.375</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>52717.24</v>
+        <v>1241.31</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Cenovus Energy Inc together with its subsidiaries develops produces refines transports and markets crude oil natural gas and refined petroleum products in Canada the United States and China</t>
+          <t>Jamieson Wellness Inc together with its subsidiaries develops manufactures distributes markets and sells the natural health products for human in Canada the United States China and internationally</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="70" customHeight="1">
+    <row r="15" ht="88" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -2534,33 +2534,33 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>CFP</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Canfor Corporation</t>
+          <t>Cenovus Energy Inc.</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Paper and Forest Products</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.316</v>
+        <v>0.345</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>1165.85</v>
+        <v>52717.24</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Canfor Corporation operates as an integrated forest products company in the United States Asia Canada Europe and internationally</t>
+          <t>Cenovus Energy Inc together with its subsidiaries develops produces refines transports and markets crude oil natural gas and refined petroleum products in Canada the United States and China</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
@@ -2575,39 +2575,39 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>KXS</t>
+          <t>CFP</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Kinaxis Inc.</t>
+          <t>Canfor Corporation</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Paper and Forest Products</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.289</v>
+        <v>0.321</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>2992.18</v>
+        <v>1165.85</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+          <t>Canfor Corporation operates as an integrated forest products company in the United States Asia Canada Europe and internationally</t>
         </is>
       </c>
       <c r="J16" s="54" t="n"/>
       <c r="K16" s="28" t="n"/>
     </row>
-    <row r="17" ht="52" customHeight="1">
+    <row r="17" ht="70" customHeight="1">
       <c r="A17" s="36" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -2616,39 +2616,39 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>KXS</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Senvest Capital Inc.</t>
+          <t>Kinaxis Inc.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.275</v>
+        <v>0.287</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>690.71</v>
+        <v>2992.18</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Senvest Capital Inc is a privately owned hedge fund sponsor</t>
+          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="70" customHeight="1">
+    <row r="18" ht="52" customHeight="1">
       <c r="A18" s="28" t="n"/>
       <c r="B18" s="126" t="inlineStr">
         <is>
@@ -2657,39 +2657,39 @@
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>GTE</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc.</t>
+          <t>Senvest Capital Inc.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.252</v>
+        <v>0.275</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>238.15</v>
+        <v>690.71</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc together with its subsidiaries is involved in the exploration and production of oil and gas properties in Colombia Canada and Ecuador</t>
+          <t>Senvest Capital Inc is a privately owned hedge fund sponsor</t>
         </is>
       </c>
       <c r="J18" s="54" t="n"/>
       <c r="K18" s="28" t="n"/>
     </row>
-    <row r="19" ht="88" customHeight="1">
+    <row r="19" ht="70" customHeight="1">
       <c r="A19" s="36" t="n"/>
       <c r="B19" s="126" t="inlineStr">
         <is>
@@ -2698,12 +2698,12 @@
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>KEL</t>
+          <t>GTE</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd.</t>
+          <t>Gran Tierra Energy Inc.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
@@ -2717,20 +2717,20 @@
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.203</v>
+        <v>0.258</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>1399.1</v>
+        <v>238.15</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
+          <t>Gran Tierra Energy Inc together with its subsidiaries is involved in the exploration and production of oil and gas properties in Colombia Canada and Ecuador</t>
         </is>
       </c>
       <c r="J19" s="53" t="n"/>
       <c r="K19" s="36" t="n"/>
     </row>
-    <row r="20" ht="70" customHeight="1">
+    <row r="20" ht="52" customHeight="1">
       <c r="A20" s="28" t="n"/>
       <c r="B20" s="126" t="inlineStr">
         <is>
@@ -2739,39 +2739,39 @@
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>WFG</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>Wall Financial Corporation</t>
+          <t>West Fraser Timber Co. Ltd.</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Real Estate Management and Development</t>
+          <t>Paper and Forest Products</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.171</v>
+        <v>0.247</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>430.47</v>
+        <v>5201.6</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>Wall Financial Corporation together with its subsidiaries operates as a real estate investment and development company in Canada</t>
+          <t>West Fraser Timber Co</t>
         </is>
       </c>
       <c r="J20" s="54" t="n"/>
       <c r="K20" s="28" t="n"/>
     </row>
-    <row r="21" ht="70" customHeight="1">
+    <row r="21" ht="88" customHeight="1">
       <c r="A21" s="36" t="n"/>
       <c r="B21" s="126" t="inlineStr">
         <is>
@@ -2780,33 +2780,33 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>EPRX</t>
+          <t>KEL</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Eupraxia Pharmaceuticals Inc.</t>
+          <t>Kelt Exploration Ltd.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.155</v>
+        <v>0.203</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>399.81</v>
+        <v>1399.1</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Eupraxia Pharmaceuticals Inc a clinical-stage biotechnology company focuses on the development of products to address therapeutic areas with unmet medical need</t>
+          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
@@ -2821,74 +2821,74 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>HWX</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Headwater Exploration Inc.</t>
+          <t>Wall Financial Corporation</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Real Estate Management and Development</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.131</v>
+        <v>0.171</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>2198.74</v>
+        <v>430.47</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Headwater Exploration Inc engages in the exploration development and production of petroleum and natural gas resources in Canada</t>
+          <t>Wall Financial Corporation together with its subsidiaries operates as a real estate investment and development company in Canada</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="106" customHeight="1">
+    <row r="23" ht="70" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B23" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>MATR</t>
+          <t>EPRX</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Mattr Corp.</t>
+          <t>Eupraxia Pharmaceuticals Inc.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Electrical Equipment</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>1.284</v>
+        <v>0.152</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>754.02</v>
+        <v>399.81</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Mattr Corp operates as a materials technology company that serves the infrastructure markets including electrification transportation mining energy communication and water management markets in Canada the United States Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Eupraxia Pharmaceuticals Inc a clinical-stage biotechnology company focuses on the development of products to address therapeutic areas with unmet medical need</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
@@ -2896,46 +2896,46 @@
     </row>
     <row r="24" ht="70" customHeight="1">
       <c r="A24" s="36" t="n"/>
-      <c r="B24" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B24" s="126" t="inlineStr">
+        <is>
+          <t>NEW</t>
         </is>
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>LGD</t>
+          <t>HWX</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Liberty Gold Corp.</t>
+          <t>Headwater Exploration Inc.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>1.067</v>
+        <v>0.129</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>521.72</v>
+        <v>2198.74</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Liberty Gold Corp engages in the acquisition exploration and development of mineral properties primarily in the United States and Türkiye</t>
+          <t>Headwater Exploration Inc engages in the exploration development and production of petroleum and natural gas resources in Canada</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="52" customHeight="1">
+    <row r="25" ht="106" customHeight="1">
       <c r="A25" s="28" t="n"/>
       <c r="B25" s="127" t="inlineStr">
         <is>
@@ -2944,33 +2944,33 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>HMMC</t>
+          <t>MATR</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Hemlo Mining Corp.</t>
+          <t>Mattr Corp.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Electrical Equipment</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.373</v>
+        <v>1.342</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>1187.51</v>
+        <v>754.02</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Hemlo Mining Corp engages in the production and operation of gold mining assets in Canada</t>
+          <t>Mattr Corp operates as a materials technology company that serves the infrastructure markets including electrification transportation mining energy communication and water management markets in Canada the United States Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
@@ -2985,190 +2985,246 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>WCP</t>
+          <t>LGD</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc.</t>
+          <t>Liberty Gold Corp.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.287</v>
+        <v>1.072</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>13692.85</v>
+        <v>521.72</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
+          <t>Liberty Gold Corp engages in the acquisition exploration and development of mineral properties primarily in the United States and Türkiye</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="70" customHeight="1">
+    <row r="27" ht="52" customHeight="1">
       <c r="A27" s="36" t="n"/>
-      <c r="B27" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
+      <c r="B27" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>HMMC</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Total Energy Services Inc.</t>
+          <t>Hemlo Mining Corp.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Energy Equipment and Services</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.698</v>
+        <v>0.37</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>627.4299999999999</v>
+        <v>1187.51</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
+          <t>Hemlo Mining Corp engages in the production and operation of gold mining assets in Canada</t>
         </is>
       </c>
       <c r="J27" s="53" t="n"/>
       <c r="K27" s="36" t="n"/>
     </row>
-    <row r="28" ht="52" customHeight="1">
+    <row r="28" ht="70" customHeight="1">
       <c r="A28" s="28" t="n"/>
-      <c r="B28" s="129" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C28" s="130" t="inlineStr">
-        <is>
-          <t>SGY</t>
-        </is>
-      </c>
-      <c r="D28" s="131" t="inlineStr">
-        <is>
-          <t>Surge Energy Inc.</t>
-        </is>
-      </c>
-      <c r="E28" s="132" t="inlineStr">
+      <c r="B28" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
+        </is>
+      </c>
+      <c r="C28" s="115" t="inlineStr">
+        <is>
+          <t>WCP</t>
+        </is>
+      </c>
+      <c r="D28" s="116" t="inlineStr">
+        <is>
+          <t>Whitecap Resources Inc.</t>
+        </is>
+      </c>
+      <c r="E28" s="117" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F28" s="132" t="inlineStr">
+      <c r="F28" s="117" t="inlineStr">
         <is>
           <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
-      <c r="G28" s="133" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="H28" s="134" t="n">
-        <v>706.29</v>
-      </c>
-      <c r="I28" s="135" t="inlineStr">
-        <is>
-          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
+      <c r="G28" s="118" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="H28" s="119" t="n">
+        <v>13692.85</v>
+      </c>
+      <c r="I28" s="120" t="inlineStr">
+        <is>
+          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
         </is>
       </c>
       <c r="J28" s="54" t="n"/>
       <c r="K28" s="28" t="n"/>
     </row>
-    <row r="29" ht="8" customHeight="1">
+    <row r="29" ht="70" customHeight="1">
       <c r="A29" s="36" t="n"/>
-      <c r="B29" s="136" t="n"/>
-      <c r="C29" s="137" t="n"/>
-      <c r="D29" s="138" t="n"/>
-      <c r="E29" s="139" t="n"/>
-      <c r="F29" s="139" t="n"/>
-      <c r="G29" s="140" t="n"/>
-      <c r="H29" s="141" t="n"/>
-      <c r="I29" s="142" t="n"/>
+      <c r="B29" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C29" s="121" t="inlineStr">
+        <is>
+          <t>TOT</t>
+        </is>
+      </c>
+      <c r="D29" s="122" t="inlineStr">
+        <is>
+          <t>Total Energy Services Inc.</t>
+        </is>
+      </c>
+      <c r="E29" s="123" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F29" s="123" t="inlineStr">
+        <is>
+          <t>Energy Equipment and Services</t>
+        </is>
+      </c>
+      <c r="G29" s="118" t="n">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="H29" s="124" t="n">
+        <v>627.4299999999999</v>
+      </c>
+      <c r="I29" s="125" t="inlineStr">
+        <is>
+          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
+        </is>
+      </c>
       <c r="J29" s="53" t="n"/>
       <c r="K29" s="36" t="n"/>
     </row>
-    <row r="30" ht="34" customHeight="1">
+    <row r="30" ht="52" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="143" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C30" s="144" t="n"/>
-      <c r="D30" s="144" t="n"/>
-      <c r="E30" s="144" t="n"/>
-      <c r="F30" s="144" t="n"/>
-      <c r="G30" s="144" t="n"/>
-      <c r="H30" s="144" t="n"/>
-      <c r="I30" s="144" t="n"/>
+      <c r="B30" s="129" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C30" s="130" t="inlineStr">
+        <is>
+          <t>SGY</t>
+        </is>
+      </c>
+      <c r="D30" s="131" t="inlineStr">
+        <is>
+          <t>Surge Energy Inc.</t>
+        </is>
+      </c>
+      <c r="E30" s="132" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F30" s="132" t="inlineStr">
+        <is>
+          <t>Oil Gas and Consumable Fuels</t>
+        </is>
+      </c>
+      <c r="G30" s="133" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="H30" s="134" t="n">
+        <v>706.29</v>
+      </c>
+      <c r="I30" s="135" t="inlineStr">
+        <is>
+          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
+        </is>
+      </c>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="28" customHeight="1">
+    <row r="31" ht="8" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="145" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C31" s="146" t="n"/>
-      <c r="D31" s="146" t="n"/>
-      <c r="E31" s="146" t="n"/>
-      <c r="F31" s="146" t="n"/>
-      <c r="G31" s="146" t="n"/>
-      <c r="H31" s="146" t="n"/>
-      <c r="I31" s="146" t="n"/>
+      <c r="B31" s="136" t="n"/>
+      <c r="C31" s="137" t="n"/>
+      <c r="D31" s="138" t="n"/>
+      <c r="E31" s="139" t="n"/>
+      <c r="F31" s="139" t="n"/>
+      <c r="G31" s="140" t="n"/>
+      <c r="H31" s="141" t="n"/>
+      <c r="I31" s="142" t="n"/>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="24" customHeight="1">
+    <row r="32" ht="34" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="48" t="n"/>
-      <c r="C32" s="38" t="n"/>
-      <c r="D32" s="39" t="n"/>
-      <c r="E32" s="40" t="n"/>
-      <c r="F32" s="40" t="n"/>
-      <c r="G32" s="89" t="n"/>
-      <c r="H32" s="91" t="n"/>
-      <c r="I32" s="53" t="n"/>
+      <c r="B32" s="143" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C32" s="144" t="n"/>
+      <c r="D32" s="144" t="n"/>
+      <c r="E32" s="144" t="n"/>
+      <c r="F32" s="144" t="n"/>
+      <c r="G32" s="144" t="n"/>
+      <c r="H32" s="144" t="n"/>
+      <c r="I32" s="144" t="n"/>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="20.4" customHeight="1">
+    <row r="33" ht="28" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="49" t="n"/>
-      <c r="C33" s="30" t="n"/>
-      <c r="D33" s="31" t="n"/>
-      <c r="E33" s="32" t="n"/>
-      <c r="F33" s="32" t="n"/>
-      <c r="G33" s="89" t="n"/>
-      <c r="H33" s="93" t="n"/>
-      <c r="I33" s="54" t="n"/>
+      <c r="B33" s="145" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C33" s="146" t="n"/>
+      <c r="D33" s="146" t="n"/>
+      <c r="E33" s="146" t="n"/>
+      <c r="F33" s="146" t="n"/>
+      <c r="G33" s="146" t="n"/>
+      <c r="H33" s="146" t="n"/>
+      <c r="I33" s="146" t="n"/>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
@@ -3383,12 +3439,12 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B30:I30"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="B32:I32"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G28">
+  <conditionalFormatting sqref="G8:G30">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -4369,7 +4425,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46281.69288846787</v>
+        <v>46281.72427577974</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4502,7 +4558,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>1.376</v>
+        <v>1.37</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>184733.62</v>
@@ -4543,7 +4599,7 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>1.109</v>
+        <v>1.115</v>
       </c>
       <c r="H9" s="124" t="n">
         <v>111614.59</v>
@@ -4584,7 +4640,7 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.603</v>
+        <v>0.626</v>
       </c>
       <c r="H10" s="119" t="n">
         <v>9525.209999999999</v>
@@ -4625,7 +4681,7 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.55</v>
+        <v>0.545</v>
       </c>
       <c r="H11" s="124" t="n">
         <v>50462.03</v>
@@ -4666,7 +4722,7 @@
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.513</v>
+        <v>0.517</v>
       </c>
       <c r="H12" s="119" t="n">
         <v>18710.64</v>
@@ -4707,7 +4763,7 @@
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.414</v>
+        <v>0.417</v>
       </c>
       <c r="H13" s="124" t="n">
         <v>23983.85</v>
@@ -4748,7 +4804,7 @@
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.408</v>
+        <v>0.412</v>
       </c>
       <c r="H14" s="119" t="n">
         <v>36459.35</v>
@@ -4789,7 +4845,7 @@
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.367</v>
+        <v>0.37</v>
       </c>
       <c r="H15" s="124" t="n">
         <v>208163.39</v>
@@ -4830,7 +4886,7 @@
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.305</v>
+        <v>0.307</v>
       </c>
       <c r="H16" s="119" t="n">
         <v>22431.33</v>
@@ -4871,7 +4927,7 @@
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.272</v>
+        <v>0.275</v>
       </c>
       <c r="H17" s="124" t="n">
         <v>25502.21</v>
@@ -4912,7 +4968,7 @@
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.267</v>
+        <v>0.268</v>
       </c>
       <c r="H18" s="119" t="n">
         <v>17599.83</v>
@@ -4953,7 +5009,7 @@
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.259</v>
+        <v>0.26</v>
       </c>
       <c r="H19" s="124" t="n">
         <v>47371.17</v>
@@ -4994,7 +5050,7 @@
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>2.621</v>
+        <v>2.596</v>
       </c>
       <c r="H20" s="119" t="n">
         <v>272918.28</v>
@@ -5035,7 +5091,7 @@
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>1.683</v>
+        <v>1.664</v>
       </c>
       <c r="H21" s="124" t="n">
         <v>63016.2</v>
@@ -5076,7 +5132,7 @@
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.859</v>
+        <v>0.864</v>
       </c>
       <c r="H22" s="119" t="n">
         <v>24056.52</v>
@@ -5117,7 +5173,7 @@
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.805</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H23" s="124" t="n">
         <v>91152.84</v>
@@ -5158,7 +5214,7 @@
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.696</v>
+        <v>0.709</v>
       </c>
       <c r="H24" s="119" t="n">
         <v>90462.64999999999</v>
@@ -5199,7 +5255,7 @@
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.697</v>
       </c>
       <c r="H25" s="124" t="n">
         <v>12100.89</v>
@@ -5240,7 +5296,7 @@
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.631</v>
+        <v>0.642</v>
       </c>
       <c r="H26" s="119" t="n">
         <v>35144.8</v>
@@ -5281,7 +5337,7 @@
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.534</v>
+        <v>0.536</v>
       </c>
       <c r="H27" s="124" t="n">
         <v>83426.56</v>
@@ -5322,7 +5378,7 @@
         </is>
       </c>
       <c r="G28" s="133" t="n">
-        <v>0.481</v>
+        <v>0.48</v>
       </c>
       <c r="H28" s="134" t="n">
         <v>16130.17</v>

--- a/outputs/benchmark-beaters/Benchmark_Beaters_2026-09-16.xlsx
+++ b/outputs/benchmark-beaters/Benchmark_Beaters_2026-09-16.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Koyfin - US" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cdn Hardcoded'!$A$1:$J$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Cdn'!$A$1:$J$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'US Hardcoded'!$A$1:$J$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'US'!$A$1:$J$54</definedName>
@@ -2071,7 +2071,7 @@
     <row r="2" ht="15.6" customHeight="1">
       <c r="A2" s="22" t="n"/>
       <c r="B2" s="21" t="n">
-        <v>46281.72427577974</v>
+        <v>46281.78359014434</v>
       </c>
       <c r="C2" s="22" t="n"/>
     </row>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46281.72427577974</v>
+        <v>46281.78359014434</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -2238,7 +2238,7 @@
       <c r="J7" s="26" t="n"/>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="52" customHeight="1">
+    <row r="8" ht="70" customHeight="1">
       <c r="A8" s="36" t="n"/>
       <c r="B8" s="126" t="inlineStr">
         <is>
@@ -2247,39 +2247,39 @@
       </c>
       <c r="C8" s="115" t="inlineStr">
         <is>
-          <t>CVVY</t>
+          <t>IFP</t>
         </is>
       </c>
       <c r="D8" s="116" t="inlineStr">
         <is>
-          <t>Cavvy Energy Ltd.</t>
+          <t>Interfor Corporation</t>
         </is>
       </c>
       <c r="E8" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F8" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Paper and Forest Products</t>
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>0.931</v>
+        <v>0.698</v>
       </c>
       <c r="H8" s="119" t="n">
-        <v>372.96</v>
+        <v>590.9299999999999</v>
       </c>
       <c r="I8" s="120" t="inlineStr">
         <is>
-          <t>Cavvy Energy Ltd operates as a midstream and upstream energy company in Canada</t>
+          <t>Interfor Corporation together with its subsidiaries produces and sells wood products in Canada the United States Japan China Taiwan and internationally</t>
         </is>
       </c>
       <c r="J8" s="53" t="n"/>
       <c r="K8" s="36" t="n"/>
     </row>
-    <row r="9" ht="70" customHeight="1">
+    <row r="9" ht="52" customHeight="1">
       <c r="A9" s="28" t="n"/>
       <c r="B9" s="126" t="inlineStr">
         <is>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="C9" s="121" t="inlineStr">
         <is>
-          <t>IFP</t>
+          <t>WDO</t>
         </is>
       </c>
       <c r="D9" s="122" t="inlineStr">
         <is>
-          <t>Interfor Corporation</t>
+          <t>Wesdome Gold Mines Ltd.</t>
         </is>
       </c>
       <c r="E9" s="123" t="inlineStr">
@@ -2303,18 +2303,18 @@
       </c>
       <c r="F9" s="123" t="inlineStr">
         <is>
-          <t>Paper and Forest Products</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>0.715</v>
+        <v>0.526</v>
       </c>
       <c r="H9" s="124" t="n">
-        <v>590.9299999999999</v>
+        <v>2723.16</v>
       </c>
       <c r="I9" s="125" t="inlineStr">
         <is>
-          <t>Interfor Corporation together with its subsidiaries produces and sells wood products in Canada the United States Japan China Taiwan and internationally</t>
+          <t>Wesdome Gold Mines Ltd mines develops and explores for gold and silver deposits in Canada</t>
         </is>
       </c>
       <c r="J9" s="54" t="n"/>
@@ -2329,12 +2329,12 @@
       </c>
       <c r="C10" s="115" t="inlineStr">
         <is>
-          <t>WDO</t>
+          <t>ORE</t>
         </is>
       </c>
       <c r="D10" s="116" t="inlineStr">
         <is>
-          <t>Wesdome Gold Mines Ltd.</t>
+          <t>Orezone Gold Corporation</t>
         </is>
       </c>
       <c r="E10" s="117" t="inlineStr">
@@ -2348,20 +2348,20 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.539</v>
+        <v>0.485</v>
       </c>
       <c r="H10" s="119" t="n">
-        <v>2723.16</v>
+        <v>1074.11</v>
       </c>
       <c r="I10" s="120" t="inlineStr">
         <is>
-          <t>Wesdome Gold Mines Ltd mines develops and explores for gold and silver deposits in Canada</t>
+          <t>Orezone Gold Corporation engages in the mining exploration and development of gold properties</t>
         </is>
       </c>
       <c r="J10" s="53" t="n"/>
       <c r="K10" s="36" t="n"/>
     </row>
-    <row r="11" ht="52" customHeight="1">
+    <row r="11" ht="70" customHeight="1">
       <c r="A11" s="28" t="n"/>
       <c r="B11" s="126" t="inlineStr">
         <is>
@@ -2370,33 +2370,33 @@
       </c>
       <c r="C11" s="121" t="inlineStr">
         <is>
-          <t>ORE</t>
+          <t>IAG</t>
         </is>
       </c>
       <c r="D11" s="122" t="inlineStr">
         <is>
-          <t>Orezone Gold Corporation</t>
+          <t>iA Financial Corporation Inc.</t>
         </is>
       </c>
       <c r="E11" s="123" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F11" s="123" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.51</v>
+        <v>0.477</v>
       </c>
       <c r="H11" s="124" t="n">
-        <v>1074.11</v>
+        <v>12965.18</v>
       </c>
       <c r="I11" s="125" t="inlineStr">
         <is>
-          <t>Orezone Gold Corporation engages in the mining exploration and development of gold properties</t>
+          <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
         </is>
       </c>
       <c r="J11" s="54" t="n"/>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="C12" s="115" t="inlineStr">
         <is>
-          <t>IAG</t>
+          <t>BNS</t>
         </is>
       </c>
       <c r="D12" s="116" t="inlineStr">
         <is>
-          <t>iA Financial Corporation Inc.</t>
+          <t>The Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="E12" s="117" t="inlineStr">
@@ -2426,24 +2426,24 @@
       </c>
       <c r="F12" s="117" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.474</v>
+        <v>0.418</v>
       </c>
       <c r="H12" s="119" t="n">
-        <v>12965.18</v>
+        <v>106366.17</v>
       </c>
       <c r="I12" s="120" t="inlineStr">
         <is>
-          <t>iA Financial Corporation Inc provides insurance and wealth management services for individual and group basis in Canada and the United States</t>
+          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
         </is>
       </c>
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="70" customHeight="1">
+    <row r="13" ht="88" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -2452,33 +2452,33 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>BNS</t>
+          <t>JWEL</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia</t>
+          <t>Jamieson Wellness Inc.</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Personal Care Products</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.422</v>
+        <v>0.375</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>106366.17</v>
+        <v>1241.31</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia provides various banking products and services in Canada the United States Mexico Peru Chile Colombia the Caribbean and Central America and internationally</t>
+          <t>Jamieson Wellness Inc together with its subsidiaries develops manufactures distributes markets and sells the natural health products for human in Canada the United States China and internationally</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
@@ -2493,39 +2493,39 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>JWEL</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Jamieson Wellness Inc.</t>
+          <t>Cenovus Energy Inc.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Personal Care Products</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.375</v>
+        <v>0.345</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>1241.31</v>
+        <v>52717.24</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Jamieson Wellness Inc together with its subsidiaries develops manufactures distributes markets and sells the natural health products for human in Canada the United States China and internationally</t>
+          <t>Cenovus Energy Inc together with its subsidiaries develops produces refines transports and markets crude oil natural gas and refined petroleum products in Canada the United States and China</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
       <c r="K14" s="36" t="n"/>
     </row>
-    <row r="15" ht="88" customHeight="1">
+    <row r="15" ht="70" customHeight="1">
       <c r="A15" s="28" t="n"/>
       <c r="B15" s="126" t="inlineStr">
         <is>
@@ -2534,33 +2534,33 @@
       </c>
       <c r="C15" s="121" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>CFP</t>
         </is>
       </c>
       <c r="D15" s="122" t="inlineStr">
         <is>
-          <t>Cenovus Energy Inc.</t>
+          <t>Canfor Corporation</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F15" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Paper and Forest Products</t>
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.345</v>
+        <v>0.311</v>
       </c>
       <c r="H15" s="124" t="n">
-        <v>52717.24</v>
+        <v>1165.85</v>
       </c>
       <c r="I15" s="125" t="inlineStr">
         <is>
-          <t>Cenovus Energy Inc together with its subsidiaries develops produces refines transports and markets crude oil natural gas and refined petroleum products in Canada the United States and China</t>
+          <t>Canfor Corporation operates as an integrated forest products company in the United States Asia Canada Europe and internationally</t>
         </is>
       </c>
       <c r="J15" s="54" t="n"/>
@@ -2575,39 +2575,39 @@
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>CFP</t>
+          <t>KXS</t>
         </is>
       </c>
       <c r="D16" s="116" t="inlineStr">
         <is>
-          <t>Canfor Corporation</t>
+          <t>Kinaxis Inc.</t>
         </is>
       </c>
       <c r="E16" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F16" s="117" t="inlineStr">
         <is>
-          <t>Paper and Forest Products</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.321</v>
+        <v>0.297</v>
       </c>
       <c r="H16" s="119" t="n">
-        <v>1165.85</v>
+        <v>2992.18</v>
       </c>
       <c r="I16" s="120" t="inlineStr">
         <is>
-          <t>Canfor Corporation operates as an integrated forest products company in the United States Asia Canada Europe and internationally</t>
+          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
         </is>
       </c>
       <c r="J16" s="54" t="n"/>
       <c r="K16" s="28" t="n"/>
     </row>
-    <row r="17" ht="70" customHeight="1">
+    <row r="17" ht="52" customHeight="1">
       <c r="A17" s="36" t="n"/>
       <c r="B17" s="126" t="inlineStr">
         <is>
@@ -2616,39 +2616,39 @@
       </c>
       <c r="C17" s="121" t="inlineStr">
         <is>
-          <t>KXS</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D17" s="122" t="inlineStr">
         <is>
-          <t>Kinaxis Inc.</t>
+          <t>Senvest Capital Inc.</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F17" s="123" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.287</v>
+        <v>0.275</v>
       </c>
       <c r="H17" s="124" t="n">
-        <v>2992.18</v>
+        <v>690.71</v>
       </c>
       <c r="I17" s="125" t="inlineStr">
         <is>
-          <t>Kinaxis Inc provides cloud-based subscription software-as-a-service for supply chain operations in the United States Europe Asia and Canada</t>
+          <t>Senvest Capital Inc is a privately owned hedge fund sponsor</t>
         </is>
       </c>
       <c r="J17" s="53" t="n"/>
       <c r="K17" s="36" t="n"/>
     </row>
-    <row r="18" ht="52" customHeight="1">
+    <row r="18" ht="70" customHeight="1">
       <c r="A18" s="28" t="n"/>
       <c r="B18" s="126" t="inlineStr">
         <is>
@@ -2657,39 +2657,39 @@
       </c>
       <c r="C18" s="115" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>GTE</t>
         </is>
       </c>
       <c r="D18" s="116" t="inlineStr">
         <is>
-          <t>Senvest Capital Inc.</t>
+          <t>Gran Tierra Energy Inc.</t>
         </is>
       </c>
       <c r="E18" s="117" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F18" s="117" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G18" s="118" t="n">
-        <v>0.275</v>
+        <v>0.262</v>
       </c>
       <c r="H18" s="119" t="n">
-        <v>690.71</v>
+        <v>238.15</v>
       </c>
       <c r="I18" s="120" t="inlineStr">
         <is>
-          <t>Senvest Capital Inc is a privately owned hedge fund sponsor</t>
+          <t>Gran Tierra Energy Inc together with its subsidiaries is involved in the exploration and production of oil and gas properties in Colombia Canada and Ecuador</t>
         </is>
       </c>
       <c r="J18" s="54" t="n"/>
       <c r="K18" s="28" t="n"/>
     </row>
-    <row r="19" ht="70" customHeight="1">
+    <row r="19" ht="88" customHeight="1">
       <c r="A19" s="36" t="n"/>
       <c r="B19" s="126" t="inlineStr">
         <is>
@@ -2698,12 +2698,12 @@
       </c>
       <c r="C19" s="121" t="inlineStr">
         <is>
-          <t>GTE</t>
+          <t>KEL</t>
         </is>
       </c>
       <c r="D19" s="122" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc.</t>
+          <t>Kelt Exploration Ltd.</t>
         </is>
       </c>
       <c r="E19" s="123" t="inlineStr">
@@ -2717,20 +2717,20 @@
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.258</v>
+        <v>0.195</v>
       </c>
       <c r="H19" s="124" t="n">
-        <v>238.15</v>
+        <v>1399.1</v>
       </c>
       <c r="I19" s="125" t="inlineStr">
         <is>
-          <t>Gran Tierra Energy Inc together with its subsidiaries is involved in the exploration and production of oil and gas properties in Colombia Canada and Ecuador</t>
+          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
         </is>
       </c>
       <c r="J19" s="53" t="n"/>
       <c r="K19" s="36" t="n"/>
     </row>
-    <row r="20" ht="52" customHeight="1">
+    <row r="20" ht="70" customHeight="1">
       <c r="A20" s="28" t="n"/>
       <c r="B20" s="126" t="inlineStr">
         <is>
@@ -2739,39 +2739,39 @@
       </c>
       <c r="C20" s="115" t="inlineStr">
         <is>
-          <t>WFG</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="D20" s="116" t="inlineStr">
         <is>
-          <t>West Fraser Timber Co. Ltd.</t>
+          <t>Wall Financial Corporation</t>
         </is>
       </c>
       <c r="E20" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F20" s="117" t="inlineStr">
         <is>
-          <t>Paper and Forest Products</t>
+          <t>Real Estate Management and Development</t>
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>0.247</v>
+        <v>0.171</v>
       </c>
       <c r="H20" s="119" t="n">
-        <v>5201.6</v>
+        <v>430.47</v>
       </c>
       <c r="I20" s="120" t="inlineStr">
         <is>
-          <t>West Fraser Timber Co</t>
+          <t>Wall Financial Corporation together with its subsidiaries operates as a real estate investment and development company in Canada</t>
         </is>
       </c>
       <c r="J20" s="54" t="n"/>
       <c r="K20" s="28" t="n"/>
     </row>
-    <row r="21" ht="88" customHeight="1">
+    <row r="21" ht="70" customHeight="1">
       <c r="A21" s="36" t="n"/>
       <c r="B21" s="126" t="inlineStr">
         <is>
@@ -2780,33 +2780,33 @@
       </c>
       <c r="C21" s="121" t="inlineStr">
         <is>
-          <t>KEL</t>
+          <t>EPRX</t>
         </is>
       </c>
       <c r="D21" s="122" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd.</t>
+          <t>Eupraxia Pharmaceuticals Inc.</t>
         </is>
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F21" s="123" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>0.203</v>
+        <v>0.153</v>
       </c>
       <c r="H21" s="124" t="n">
-        <v>1399.1</v>
+        <v>399.81</v>
       </c>
       <c r="I21" s="125" t="inlineStr">
         <is>
-          <t>Kelt Exploration Ltd an oil and gas company engages in the exploration development and production of crude oil and natural gas resources natural gas primarily in Northwestern Alberta and Northeastern British Columbia</t>
+          <t>Eupraxia Pharmaceuticals Inc a clinical-stage biotechnology company focuses on the development of products to address therapeutic areas with unmet medical need</t>
         </is>
       </c>
       <c r="J21" s="53" t="n"/>
@@ -2821,74 +2821,74 @@
       </c>
       <c r="C22" s="115" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>HWX</t>
         </is>
       </c>
       <c r="D22" s="116" t="inlineStr">
         <is>
-          <t>Wall Financial Corporation</t>
+          <t>Headwater Exploration Inc.</t>
         </is>
       </c>
       <c r="E22" s="117" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F22" s="117" t="inlineStr">
         <is>
-          <t>Real Estate Management and Development</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.171</v>
+        <v>0.12</v>
       </c>
       <c r="H22" s="119" t="n">
-        <v>430.47</v>
+        <v>2198.74</v>
       </c>
       <c r="I22" s="120" t="inlineStr">
         <is>
-          <t>Wall Financial Corporation together with its subsidiaries operates as a real estate investment and development company in Canada</t>
+          <t>Headwater Exploration Inc engages in the exploration development and production of petroleum and natural gas resources in Canada</t>
         </is>
       </c>
       <c r="J22" s="54" t="n"/>
       <c r="K22" s="28" t="n"/>
     </row>
-    <row r="23" ht="70" customHeight="1">
+    <row r="23" ht="106" customHeight="1">
       <c r="A23" s="28" t="n"/>
-      <c r="B23" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B23" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C23" s="121" t="inlineStr">
         <is>
-          <t>EPRX</t>
+          <t>MATR</t>
         </is>
       </c>
       <c r="D23" s="122" t="inlineStr">
         <is>
-          <t>Eupraxia Pharmaceuticals Inc.</t>
+          <t>Mattr Corp.</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F23" s="123" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Electrical Equipment</t>
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.152</v>
+        <v>1.328</v>
       </c>
       <c r="H23" s="124" t="n">
-        <v>399.81</v>
+        <v>754.02</v>
       </c>
       <c r="I23" s="125" t="inlineStr">
         <is>
-          <t>Eupraxia Pharmaceuticals Inc a clinical-stage biotechnology company focuses on the development of products to address therapeutic areas with unmet medical need</t>
+          <t>Mattr Corp operates as a materials technology company that serves the infrastructure markets including electrification transportation mining energy communication and water management markets in Canada the United States Europe the Middle East Africa and the Asia Pacific</t>
         </is>
       </c>
       <c r="J23" s="54" t="n"/>
@@ -2896,46 +2896,46 @@
     </row>
     <row r="24" ht="70" customHeight="1">
       <c r="A24" s="36" t="n"/>
-      <c r="B24" s="126" t="inlineStr">
-        <is>
-          <t>NEW</t>
+      <c r="B24" s="127" t="inlineStr">
+        <is>
+          <t>RPT</t>
         </is>
       </c>
       <c r="C24" s="115" t="inlineStr">
         <is>
-          <t>HWX</t>
+          <t>LGD</t>
         </is>
       </c>
       <c r="D24" s="116" t="inlineStr">
         <is>
-          <t>Headwater Exploration Inc.</t>
+          <t>Liberty Gold Corp.</t>
         </is>
       </c>
       <c r="E24" s="117" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F24" s="117" t="inlineStr">
         <is>
-          <t>Oil Gas and Consumable Fuels</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.129</v>
+        <v>1.113</v>
       </c>
       <c r="H24" s="119" t="n">
-        <v>2198.74</v>
+        <v>521.72</v>
       </c>
       <c r="I24" s="120" t="inlineStr">
         <is>
-          <t>Headwater Exploration Inc engages in the exploration development and production of petroleum and natural gas resources in Canada</t>
+          <t>Liberty Gold Corp engages in the acquisition exploration and development of mineral properties primarily in the United States and Türkiye</t>
         </is>
       </c>
       <c r="J24" s="53" t="n"/>
       <c r="K24" s="36" t="n"/>
     </row>
-    <row r="25" ht="106" customHeight="1">
+    <row r="25" ht="52" customHeight="1">
       <c r="A25" s="28" t="n"/>
       <c r="B25" s="127" t="inlineStr">
         <is>
@@ -2944,33 +2944,33 @@
       </c>
       <c r="C25" s="121" t="inlineStr">
         <is>
-          <t>MATR</t>
+          <t>HMMC</t>
         </is>
       </c>
       <c r="D25" s="122" t="inlineStr">
         <is>
-          <t>Mattr Corp.</t>
+          <t>Hemlo Mining Corp.</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F25" s="123" t="inlineStr">
         <is>
-          <t>Electrical Equipment</t>
+          <t>Metals and Mining</t>
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>1.342</v>
+        <v>0.347</v>
       </c>
       <c r="H25" s="124" t="n">
-        <v>754.02</v>
+        <v>1187.51</v>
       </c>
       <c r="I25" s="125" t="inlineStr">
         <is>
-          <t>Mattr Corp operates as a materials technology company that serves the infrastructure markets including electrification transportation mining energy communication and water management markets in Canada the United States Europe the Middle East Africa and the Asia Pacific</t>
+          <t>Hemlo Mining Corp engages in the production and operation of gold mining assets in Canada</t>
         </is>
       </c>
       <c r="J25" s="54" t="n"/>
@@ -2985,246 +2985,190 @@
       </c>
       <c r="C26" s="115" t="inlineStr">
         <is>
-          <t>LGD</t>
+          <t>WCP</t>
         </is>
       </c>
       <c r="D26" s="116" t="inlineStr">
         <is>
-          <t>Liberty Gold Corp.</t>
+          <t>Whitecap Resources Inc.</t>
         </is>
       </c>
       <c r="E26" s="117" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F26" s="117" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>1.072</v>
+        <v>0.275</v>
       </c>
       <c r="H26" s="119" t="n">
-        <v>521.72</v>
+        <v>13692.85</v>
       </c>
       <c r="I26" s="120" t="inlineStr">
         <is>
-          <t>Liberty Gold Corp engages in the acquisition exploration and development of mineral properties primarily in the United States and Türkiye</t>
+          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
         </is>
       </c>
       <c r="J26" s="53" t="n"/>
       <c r="K26" s="36" t="n"/>
     </row>
-    <row r="27" ht="52" customHeight="1">
+    <row r="27" ht="70" customHeight="1">
       <c r="A27" s="36" t="n"/>
-      <c r="B27" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
+      <c r="B27" s="128" t="inlineStr">
+        <is>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C27" s="121" t="inlineStr">
         <is>
-          <t>HMMC</t>
+          <t>TOT</t>
         </is>
       </c>
       <c r="D27" s="122" t="inlineStr">
         <is>
-          <t>Hemlo Mining Corp.</t>
+          <t>Total Energy Services Inc.</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F27" s="123" t="inlineStr">
         <is>
-          <t>Metals and Mining</t>
+          <t>Energy Equipment and Services</t>
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.37</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H27" s="124" t="n">
-        <v>1187.51</v>
+        <v>627.4299999999999</v>
       </c>
       <c r="I27" s="125" t="inlineStr">
         <is>
-          <t>Hemlo Mining Corp engages in the production and operation of gold mining assets in Canada</t>
+          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
         </is>
       </c>
       <c r="J27" s="53" t="n"/>
       <c r="K27" s="36" t="n"/>
     </row>
-    <row r="28" ht="70" customHeight="1">
+    <row r="28" ht="52" customHeight="1">
       <c r="A28" s="28" t="n"/>
-      <c r="B28" s="127" t="inlineStr">
-        <is>
-          <t>RPT</t>
-        </is>
-      </c>
-      <c r="C28" s="115" t="inlineStr">
-        <is>
-          <t>WCP</t>
-        </is>
-      </c>
-      <c r="D28" s="116" t="inlineStr">
-        <is>
-          <t>Whitecap Resources Inc.</t>
-        </is>
-      </c>
-      <c r="E28" s="117" t="inlineStr">
+      <c r="B28" s="129" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="C28" s="130" t="inlineStr">
+        <is>
+          <t>SGY</t>
+        </is>
+      </c>
+      <c r="D28" s="131" t="inlineStr">
+        <is>
+          <t>Surge Energy Inc.</t>
+        </is>
+      </c>
+      <c r="E28" s="132" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="F28" s="117" t="inlineStr">
+      <c r="F28" s="132" t="inlineStr">
         <is>
           <t>Oil Gas and Consumable Fuels</t>
         </is>
       </c>
-      <c r="G28" s="118" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="H28" s="119" t="n">
-        <v>13692.85</v>
-      </c>
-      <c r="I28" s="120" t="inlineStr">
-        <is>
-          <t>Whitecap Resources Inc engages in the acquisition development and holding of interests in petroleum and natural gas properties and assets in Western Canada</t>
+      <c r="G28" s="133" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="H28" s="134" t="n">
+        <v>706.29</v>
+      </c>
+      <c r="I28" s="135" t="inlineStr">
+        <is>
+          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
         </is>
       </c>
       <c r="J28" s="54" t="n"/>
       <c r="K28" s="28" t="n"/>
     </row>
-    <row r="29" ht="70" customHeight="1">
+    <row r="29" ht="8" customHeight="1">
       <c r="A29" s="36" t="n"/>
-      <c r="B29" s="128" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C29" s="121" t="inlineStr">
-        <is>
-          <t>TOT</t>
-        </is>
-      </c>
-      <c r="D29" s="122" t="inlineStr">
-        <is>
-          <t>Total Energy Services Inc.</t>
-        </is>
-      </c>
-      <c r="E29" s="123" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F29" s="123" t="inlineStr">
-        <is>
-          <t>Energy Equipment and Services</t>
-        </is>
-      </c>
-      <c r="G29" s="118" t="n">
-        <v>0.6929999999999999</v>
-      </c>
-      <c r="H29" s="124" t="n">
-        <v>627.4299999999999</v>
-      </c>
-      <c r="I29" s="125" t="inlineStr">
-        <is>
-          <t>Total Energy Services Inc operates as an energy services company primarily in Canada the United States Australia and internationally</t>
-        </is>
-      </c>
+      <c r="B29" s="136" t="n"/>
+      <c r="C29" s="137" t="n"/>
+      <c r="D29" s="138" t="n"/>
+      <c r="E29" s="139" t="n"/>
+      <c r="F29" s="139" t="n"/>
+      <c r="G29" s="140" t="n"/>
+      <c r="H29" s="141" t="n"/>
+      <c r="I29" s="142" t="n"/>
       <c r="J29" s="53" t="n"/>
       <c r="K29" s="36" t="n"/>
     </row>
-    <row r="30" ht="52" customHeight="1">
+    <row r="30" ht="34" customHeight="1">
       <c r="A30" s="36" t="n"/>
-      <c r="B30" s="129" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="C30" s="130" t="inlineStr">
-        <is>
-          <t>SGY</t>
-        </is>
-      </c>
-      <c r="D30" s="131" t="inlineStr">
-        <is>
-          <t>Surge Energy Inc.</t>
-        </is>
-      </c>
-      <c r="E30" s="132" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F30" s="132" t="inlineStr">
-        <is>
-          <t>Oil Gas and Consumable Fuels</t>
-        </is>
-      </c>
-      <c r="G30" s="133" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="H30" s="134" t="n">
-        <v>706.29</v>
-      </c>
-      <c r="I30" s="135" t="inlineStr">
-        <is>
-          <t>Surge Energy Inc engages in the exploration development and production of oil and gas properties in Western Canada</t>
-        </is>
-      </c>
+      <c r="B30" s="143" t="inlineStr">
+        <is>
+          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
+        </is>
+      </c>
+      <c r="C30" s="144" t="n"/>
+      <c r="D30" s="144" t="n"/>
+      <c r="E30" s="144" t="n"/>
+      <c r="F30" s="144" t="n"/>
+      <c r="G30" s="144" t="n"/>
+      <c r="H30" s="144" t="n"/>
+      <c r="I30" s="144" t="n"/>
       <c r="J30" s="53" t="n"/>
       <c r="K30" s="36" t="n"/>
     </row>
-    <row r="31" ht="8" customHeight="1">
+    <row r="31" ht="28" customHeight="1">
       <c r="A31" s="28" t="n"/>
-      <c r="B31" s="136" t="n"/>
-      <c r="C31" s="137" t="n"/>
-      <c r="D31" s="138" t="n"/>
-      <c r="E31" s="139" t="n"/>
-      <c r="F31" s="139" t="n"/>
-      <c r="G31" s="140" t="n"/>
-      <c r="H31" s="141" t="n"/>
-      <c r="I31" s="142" t="n"/>
+      <c r="B31" s="145" t="inlineStr">
+        <is>
+          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
+        </is>
+      </c>
+      <c r="C31" s="146" t="n"/>
+      <c r="D31" s="146" t="n"/>
+      <c r="E31" s="146" t="n"/>
+      <c r="F31" s="146" t="n"/>
+      <c r="G31" s="146" t="n"/>
+      <c r="H31" s="146" t="n"/>
+      <c r="I31" s="146" t="n"/>
       <c r="J31" s="54" t="n"/>
       <c r="K31" s="28" t="n"/>
     </row>
-    <row r="32" ht="34" customHeight="1">
+    <row r="32" ht="24" customHeight="1">
       <c r="A32" s="36" t="n"/>
-      <c r="B32" s="143" t="inlineStr">
-        <is>
-          <t>🔓 Want to know which of these we would actually buy? Start your 14-Day Free Trial at www.5iresearch.ca/bb</t>
-        </is>
-      </c>
-      <c r="C32" s="144" t="n"/>
-      <c r="D32" s="144" t="n"/>
-      <c r="E32" s="144" t="n"/>
-      <c r="F32" s="144" t="n"/>
-      <c r="G32" s="144" t="n"/>
-      <c r="H32" s="144" t="n"/>
-      <c r="I32" s="144" t="n"/>
+      <c r="B32" s="48" t="n"/>
+      <c r="C32" s="38" t="n"/>
+      <c r="D32" s="39" t="n"/>
+      <c r="E32" s="40" t="n"/>
+      <c r="F32" s="40" t="n"/>
+      <c r="G32" s="89" t="n"/>
+      <c r="H32" s="91" t="n"/>
+      <c r="I32" s="53" t="n"/>
       <c r="J32" s="53" t="n"/>
       <c r="K32" s="36" t="n"/>
     </row>
-    <row r="33" ht="28" customHeight="1">
+    <row r="33" ht="20.4" customHeight="1">
       <c r="A33" s="28" t="n"/>
-      <c r="B33" s="145" t="inlineStr">
-        <is>
-          <t>Disclosure: While this table does not constitute any formal opinion on names presented, authors may own shares in non-Canadian securities listed above.</t>
-        </is>
-      </c>
-      <c r="C33" s="146" t="n"/>
-      <c r="D33" s="146" t="n"/>
-      <c r="E33" s="146" t="n"/>
-      <c r="F33" s="146" t="n"/>
-      <c r="G33" s="146" t="n"/>
-      <c r="H33" s="146" t="n"/>
-      <c r="I33" s="146" t="n"/>
+      <c r="B33" s="49" t="n"/>
+      <c r="C33" s="30" t="n"/>
+      <c r="D33" s="31" t="n"/>
+      <c r="E33" s="32" t="n"/>
+      <c r="F33" s="32" t="n"/>
+      <c r="G33" s="89" t="n"/>
+      <c r="H33" s="93" t="n"/>
+      <c r="I33" s="54" t="n"/>
       <c r="J33" s="54" t="n"/>
       <c r="K33" s="28" t="n"/>
     </row>
@@ -3439,12 +3383,12 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B30:I30"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B33:I33"/>
-    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B31:I31"/>
     <mergeCell ref="B6:G6"/>
   </mergeCells>
-  <conditionalFormatting sqref="G8:G30">
+  <conditionalFormatting sqref="G8:G28">
     <cfRule type="colorScale" priority="1371">
       <colorScale>
         <cfvo type="min"/>
@@ -4425,7 +4369,7 @@
         </is>
       </c>
       <c r="H2" s="84" t="n">
-        <v>46281.72427577974</v>
+        <v>46281.78359014434</v>
       </c>
       <c r="J2" s="83" t="n"/>
     </row>
@@ -4558,7 +4502,7 @@
         </is>
       </c>
       <c r="G8" s="118" t="n">
-        <v>1.37</v>
+        <v>1.373</v>
       </c>
       <c r="H8" s="119" t="n">
         <v>184733.62</v>
@@ -4599,7 +4543,7 @@
         </is>
       </c>
       <c r="G9" s="118" t="n">
-        <v>1.115</v>
+        <v>1.122</v>
       </c>
       <c r="H9" s="124" t="n">
         <v>111614.59</v>
@@ -4640,7 +4584,7 @@
         </is>
       </c>
       <c r="G10" s="118" t="n">
-        <v>0.626</v>
+        <v>0.601</v>
       </c>
       <c r="H10" s="119" t="n">
         <v>9525.209999999999</v>
@@ -4681,7 +4625,7 @@
         </is>
       </c>
       <c r="G11" s="118" t="n">
-        <v>0.545</v>
+        <v>0.527</v>
       </c>
       <c r="H11" s="124" t="n">
         <v>50462.03</v>
@@ -4722,7 +4666,7 @@
         </is>
       </c>
       <c r="G12" s="118" t="n">
-        <v>0.517</v>
+        <v>0.513</v>
       </c>
       <c r="H12" s="119" t="n">
         <v>18710.64</v>
@@ -4735,7 +4679,7 @@
       <c r="J12" s="53" t="n"/>
       <c r="K12" s="36" t="n"/>
     </row>
-    <row r="13" ht="70" customHeight="1">
+    <row r="13" ht="52" customHeight="1">
       <c r="A13" s="28" t="n"/>
       <c r="B13" s="126" t="inlineStr">
         <is>
@@ -4744,39 +4688,39 @@
       </c>
       <c r="C13" s="121" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="D13" s="122" t="inlineStr">
         <is>
-          <t>Principal Financial Group Inc.</t>
+          <t>Waters Corporation</t>
         </is>
       </c>
       <c r="E13" s="123" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F13" s="123" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Life Sciences Tools and Services</t>
         </is>
       </c>
       <c r="G13" s="118" t="n">
-        <v>0.417</v>
+        <v>0.416</v>
       </c>
       <c r="H13" s="124" t="n">
-        <v>23983.85</v>
+        <v>36459.35</v>
       </c>
       <c r="I13" s="125" t="inlineStr">
         <is>
-          <t>Principal Financial Group Inc provides retirement asset management and insurance products and services to businesses individuals and institutional clients worldwide</t>
+          <t>Waters Corporation provides analytical workflow solutions in Asia the Americas and Europe</t>
         </is>
       </c>
       <c r="J13" s="54" t="n"/>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="52" customHeight="1">
+    <row r="14" ht="70" customHeight="1">
       <c r="A14" s="36" t="n"/>
       <c r="B14" s="126" t="inlineStr">
         <is>
@@ -4785,33 +4729,33 @@
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="D14" s="116" t="inlineStr">
         <is>
-          <t>Waters Corporation</t>
+          <t>Principal Financial Group Inc.</t>
         </is>
       </c>
       <c r="E14" s="117" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F14" s="117" t="inlineStr">
         <is>
-          <t>Life Sciences Tools and Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="G14" s="118" t="n">
-        <v>0.412</v>
+        <v>0.405</v>
       </c>
       <c r="H14" s="119" t="n">
-        <v>36459.35</v>
+        <v>23983.85</v>
       </c>
       <c r="I14" s="120" t="inlineStr">
         <is>
-          <t>Waters Corporation provides analytical workflow solutions in Asia the Americas and Europe</t>
+          <t>Principal Financial Group Inc provides retirement asset management and insurance products and services to businesses individuals and institutional clients worldwide</t>
         </is>
       </c>
       <c r="J14" s="53" t="n"/>
@@ -4845,7 +4789,7 @@
         </is>
       </c>
       <c r="G15" s="118" t="n">
-        <v>0.37</v>
+        <v>0.377</v>
       </c>
       <c r="H15" s="124" t="n">
         <v>208163.39</v>
@@ -4886,7 +4830,7 @@
         </is>
       </c>
       <c r="G16" s="118" t="n">
-        <v>0.307</v>
+        <v>0.31</v>
       </c>
       <c r="H16" s="119" t="n">
         <v>22431.33</v>
@@ -4927,7 +4871,7 @@
         </is>
       </c>
       <c r="G17" s="118" t="n">
-        <v>0.275</v>
+        <v>0.274</v>
       </c>
       <c r="H17" s="124" t="n">
         <v>25502.21</v>
@@ -5009,7 +4953,7 @@
         </is>
       </c>
       <c r="G19" s="118" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="H19" s="124" t="n">
         <v>47371.17</v>
@@ -5050,7 +4994,7 @@
         </is>
       </c>
       <c r="G20" s="118" t="n">
-        <v>2.596</v>
+        <v>2.579</v>
       </c>
       <c r="H20" s="119" t="n">
         <v>272918.28</v>
@@ -5091,7 +5035,7 @@
         </is>
       </c>
       <c r="G21" s="118" t="n">
-        <v>1.664</v>
+        <v>1.654</v>
       </c>
       <c r="H21" s="124" t="n">
         <v>63016.2</v>
@@ -5132,7 +5076,7 @@
         </is>
       </c>
       <c r="G22" s="118" t="n">
-        <v>0.864</v>
+        <v>0.862</v>
       </c>
       <c r="H22" s="119" t="n">
         <v>24056.52</v>
@@ -5173,7 +5117,7 @@
         </is>
       </c>
       <c r="G23" s="118" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.794</v>
       </c>
       <c r="H23" s="124" t="n">
         <v>91152.84</v>
@@ -5214,7 +5158,7 @@
         </is>
       </c>
       <c r="G24" s="118" t="n">
-        <v>0.709</v>
+        <v>0.702</v>
       </c>
       <c r="H24" s="119" t="n">
         <v>90462.64999999999</v>
@@ -5255,7 +5199,7 @@
         </is>
       </c>
       <c r="G25" s="118" t="n">
-        <v>0.697</v>
+        <v>0.711</v>
       </c>
       <c r="H25" s="124" t="n">
         <v>12100.89</v>
@@ -5296,7 +5240,7 @@
         </is>
       </c>
       <c r="G26" s="118" t="n">
-        <v>0.642</v>
+        <v>0.644</v>
       </c>
       <c r="H26" s="119" t="n">
         <v>35144.8</v>
@@ -5337,7 +5281,7 @@
         </is>
       </c>
       <c r="G27" s="118" t="n">
-        <v>0.536</v>
+        <v>0.533</v>
       </c>
       <c r="H27" s="124" t="n">
         <v>83426.56</v>
@@ -5378,7 +5322,7 @@
         </is>
       </c>
       <c r="G28" s="133" t="n">
-        <v>0.48</v>
+        <v>0.494</v>
       </c>
       <c r="H28" s="134" t="n">
         <v>16130.17</v>
